--- a/artfynd/A 16101-2026 artfynd.xlsx
+++ b/artfynd/A 16101-2026 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>133099239</v>
       </c>
       <c r="B3" t="n">
-        <v>57958</v>
+        <v>57975</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>133098989</v>
       </c>
       <c r="B4" t="n">
-        <v>57958</v>
+        <v>57975</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>133098993</v>
       </c>
       <c r="B5" t="n">
-        <v>57958</v>
+        <v>57975</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>133098987</v>
       </c>
       <c r="B6" t="n">
-        <v>57958</v>
+        <v>57975</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>133098996</v>
       </c>
       <c r="B10" t="n">
-        <v>57958</v>
+        <v>57975</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>133099246</v>
       </c>
       <c r="B11" t="n">
-        <v>57958</v>
+        <v>57975</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>133099245</v>
       </c>
       <c r="B12" t="n">
-        <v>57958</v>
+        <v>57975</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1800,7 +1800,7 @@
         <v>133098991</v>
       </c>
       <c r="B13" t="n">
-        <v>57958</v>
+        <v>57975</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
         <v>133098986</v>
       </c>
       <c r="B14" t="n">
-        <v>57958</v>
+        <v>57975</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -3265,7 +3265,7 @@
         <v>133099257</v>
       </c>
       <c r="B28" t="n">
-        <v>57958</v>
+        <v>57975</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3367,7 +3367,7 @@
         <v>133099237</v>
       </c>
       <c r="B29" t="n">
-        <v>57958</v>
+        <v>57975</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
         <v>133099236</v>
       </c>
       <c r="B30" t="n">
-        <v>57958</v>
+        <v>57975</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3571,7 +3571,7 @@
         <v>133098997</v>
       </c>
       <c r="B31" t="n">
-        <v>57958</v>
+        <v>57975</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4077,7 +4077,7 @@
         <v>133099244</v>
       </c>
       <c r="B36" t="n">
-        <v>57958</v>
+        <v>57975</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4179,7 +4179,7 @@
         <v>133099252</v>
       </c>
       <c r="B37" t="n">
-        <v>57958</v>
+        <v>57975</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4281,7 +4281,7 @@
         <v>133098983</v>
       </c>
       <c r="B38" t="n">
-        <v>57958</v>
+        <v>57975</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4776,7 +4776,7 @@
         <v>133099248</v>
       </c>
       <c r="B43" t="n">
-        <v>57958</v>
+        <v>57975</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5169,7 +5169,7 @@
         <v>133099249</v>
       </c>
       <c r="B47" t="n">
-        <v>57958</v>
+        <v>57975</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5853,7 +5853,7 @@
         <v>133099235</v>
       </c>
       <c r="B54" t="n">
-        <v>57958</v>
+        <v>57975</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5955,7 +5955,7 @@
         <v>133098984</v>
       </c>
       <c r="B55" t="n">
-        <v>57958</v>
+        <v>57975</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6348,7 +6348,7 @@
         <v>133099256</v>
       </c>
       <c r="B59" t="n">
-        <v>57958</v>
+        <v>57975</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6450,7 +6450,7 @@
         <v>133099243</v>
       </c>
       <c r="B60" t="n">
-        <v>57958</v>
+        <v>57975</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6940,7 +6940,7 @@
         <v>133099253</v>
       </c>
       <c r="B65" t="n">
-        <v>57958</v>
+        <v>57975</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7527,7 +7527,7 @@
         <v>133099258</v>
       </c>
       <c r="B71" t="n">
-        <v>57958</v>
+        <v>57975</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7629,7 +7629,7 @@
         <v>133099002</v>
       </c>
       <c r="B72" t="n">
-        <v>57958</v>
+        <v>57975</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7731,7 +7731,7 @@
         <v>133099241</v>
       </c>
       <c r="B73" t="n">
-        <v>57958</v>
+        <v>57975</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7833,7 +7833,7 @@
         <v>133099238</v>
       </c>
       <c r="B74" t="n">
-        <v>57958</v>
+        <v>57975</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8425,7 +8425,7 @@
         <v>133099255</v>
       </c>
       <c r="B80" t="n">
-        <v>57958</v>
+        <v>57975</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8527,7 +8527,7 @@
         <v>133099242</v>
       </c>
       <c r="B81" t="n">
-        <v>57958</v>
+        <v>57975</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8823,7 +8823,7 @@
         <v>133099251</v>
       </c>
       <c r="B84" t="n">
-        <v>57958</v>
+        <v>57975</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9022,7 +9022,7 @@
         <v>133099240</v>
       </c>
       <c r="B86" t="n">
-        <v>57958</v>
+        <v>57975</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9344,7 +9344,7 @@
         <v>133099250</v>
       </c>
       <c r="B89" t="n">
-        <v>57958</v>
+        <v>57975</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9961,7 +9961,7 @@
         <v>133099234</v>
       </c>
       <c r="B95" t="n">
-        <v>57958</v>
+        <v>57975</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10063,7 +10063,7 @@
         <v>133098994</v>
       </c>
       <c r="B96" t="n">
-        <v>57958</v>
+        <v>57975</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10165,7 +10165,7 @@
         <v>133098990</v>
       </c>
       <c r="B97" t="n">
-        <v>57958</v>
+        <v>57975</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10461,7 +10461,7 @@
         <v>133099254</v>
       </c>
       <c r="B100" t="n">
-        <v>57958</v>
+        <v>57975</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>

--- a/artfynd/A 16101-2026 artfynd.xlsx
+++ b/artfynd/A 16101-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133099308</v>
+        <v>133099216</v>
       </c>
       <c r="B2" t="n">
-        <v>83311</v>
+        <v>97435</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>308</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>482973</v>
+        <v>482737</v>
       </c>
       <c r="R2" t="n">
-        <v>7040030</v>
+        <v>7040092</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133099239</v>
+        <v>133099274</v>
       </c>
       <c r="B3" t="n">
-        <v>57975</v>
+        <v>91924</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>112</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>482757</v>
+        <v>482818</v>
       </c>
       <c r="R3" t="n">
-        <v>7040498</v>
+        <v>7040137</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -843,11 +843,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-05-03</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133098989</v>
+        <v>133099307</v>
       </c>
       <c r="B4" t="n">
-        <v>57975</v>
+        <v>83350</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>308</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>482742</v>
+        <v>482915</v>
       </c>
       <c r="R4" t="n">
-        <v>7040155</v>
+        <v>7040050</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -945,11 +940,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-05-03</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -976,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133098993</v>
+        <v>133099308</v>
       </c>
       <c r="B5" t="n">
-        <v>57975</v>
+        <v>83350</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -987,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>308</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1011,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>482790</v>
+        <v>482973</v>
       </c>
       <c r="R5" t="n">
-        <v>7040409</v>
+        <v>7040030</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1047,11 +1037,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-05-03</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1078,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133098987</v>
+        <v>133099309</v>
       </c>
       <c r="B6" t="n">
-        <v>57975</v>
+        <v>83350</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1089,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>308</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1113,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>482747</v>
+        <v>482940</v>
       </c>
       <c r="R6" t="n">
-        <v>7040142</v>
+        <v>7040038</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1149,11 +1134,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2026-05-03</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1180,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133099220</v>
+        <v>133099275</v>
       </c>
       <c r="B7" t="n">
-        <v>91928</v>
+        <v>83349</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>492</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1215,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>482743</v>
+        <v>482908</v>
       </c>
       <c r="R7" t="n">
-        <v>7040082</v>
+        <v>7040032</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1277,32 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133099311</v>
+        <v>133099277</v>
       </c>
       <c r="B8" t="n">
-        <v>92624</v>
+        <v>92245</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>898</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1312,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>482790</v>
+        <v>482910</v>
       </c>
       <c r="R8" t="n">
-        <v>7040011</v>
+        <v>7040174</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1374,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133099306</v>
+        <v>133099279</v>
       </c>
       <c r="B9" t="n">
-        <v>79334</v>
+        <v>92245</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1385,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1409,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>482783</v>
+        <v>483036</v>
       </c>
       <c r="R9" t="n">
-        <v>7040050</v>
+        <v>7040043</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1471,65 +1451,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133098996</v>
+        <v>133099311</v>
       </c>
       <c r="B10" t="n">
-        <v>57975</v>
+        <v>92689</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>898</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Fr.) Vesterholt</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Johanssonsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>482964</v>
+        <v>482790</v>
       </c>
       <c r="R10" t="n">
-        <v>7040289</v>
+        <v>7040011</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1562,11 +1522,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2026-05-03</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Trummande födosökande hona</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1593,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133099246</v>
+        <v>133099018</v>
       </c>
       <c r="B11" t="n">
-        <v>57975</v>
+        <v>91970</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1604,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1628,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>482890</v>
+        <v>482859</v>
       </c>
       <c r="R11" t="n">
-        <v>7040433</v>
+        <v>7040251</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1664,11 +1619,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2026-05-03</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1695,10 +1645,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133099245</v>
+        <v>133099019</v>
       </c>
       <c r="B12" t="n">
-        <v>57975</v>
+        <v>91970</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1706,21 +1656,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1730,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>482765</v>
+        <v>482859</v>
       </c>
       <c r="R12" t="n">
-        <v>7040428</v>
+        <v>7039916</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1766,11 +1716,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-05-03</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1797,10 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133098991</v>
+        <v>133099020</v>
       </c>
       <c r="B13" t="n">
-        <v>57975</v>
+        <v>91970</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1808,21 +1753,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1832,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>482715</v>
+        <v>482765</v>
       </c>
       <c r="R13" t="n">
-        <v>7040181</v>
+        <v>7039995</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1868,11 +1813,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-05-03</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1899,10 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133098986</v>
+        <v>133099021</v>
       </c>
       <c r="B14" t="n">
-        <v>57975</v>
+        <v>91970</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1910,21 +1850,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1934,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>482755</v>
+        <v>482718</v>
       </c>
       <c r="R14" t="n">
-        <v>7040271</v>
+        <v>7040049</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1970,11 +1910,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-05-03</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2001,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133099274</v>
+        <v>133099283</v>
       </c>
       <c r="B15" t="n">
-        <v>91878</v>
+        <v>91970</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2012,21 +1947,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>112</v>
+        <v>1108</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2036,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>482818</v>
+        <v>482817</v>
       </c>
       <c r="R15" t="n">
-        <v>7040137</v>
+        <v>7040296</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2098,32 +2033,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133099231</v>
+        <v>133099285</v>
       </c>
       <c r="B16" t="n">
-        <v>92651</v>
+        <v>91970</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3298</v>
+        <v>1108</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2133,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>482934</v>
+        <v>483006</v>
       </c>
       <c r="R16" t="n">
-        <v>7040260</v>
+        <v>7040340</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2195,10 +2130,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133099305</v>
+        <v>133099287</v>
       </c>
       <c r="B17" t="n">
-        <v>79334</v>
+        <v>91970</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2206,21 +2141,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2230,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>482848</v>
+        <v>483086</v>
       </c>
       <c r="R17" t="n">
-        <v>7039978</v>
+        <v>7040200</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2292,10 +2227,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133099023</v>
+        <v>133099288</v>
       </c>
       <c r="B18" t="n">
-        <v>91942</v>
+        <v>91970</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2303,21 +2238,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1204</v>
+        <v>1108</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2327,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>482930</v>
+        <v>483034</v>
       </c>
       <c r="R18" t="n">
-        <v>7040057</v>
+        <v>7040042</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2389,10 +2324,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133099309</v>
+        <v>133099289</v>
       </c>
       <c r="B19" t="n">
-        <v>83311</v>
+        <v>91970</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2400,21 +2335,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>308</v>
+        <v>1108</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2424,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>482940</v>
+        <v>483011</v>
       </c>
       <c r="R19" t="n">
-        <v>7040038</v>
+        <v>7040039</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2486,10 +2421,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133099297</v>
+        <v>133099290</v>
       </c>
       <c r="B20" t="n">
-        <v>91942</v>
+        <v>91970</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2497,21 +2432,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1204</v>
+        <v>1108</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2521,10 +2456,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>482745</v>
+        <v>482948</v>
       </c>
       <c r="R20" t="n">
-        <v>7040056</v>
+        <v>7040035</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2583,32 +2518,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133099218</v>
+        <v>133099291</v>
       </c>
       <c r="B21" t="n">
-        <v>91891</v>
+        <v>91970</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5447</v>
+        <v>1108</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2618,10 +2553,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>482924</v>
+        <v>482854</v>
       </c>
       <c r="R21" t="n">
-        <v>7040053</v>
+        <v>7039929</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2680,10 +2615,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133099304</v>
+        <v>133099292</v>
       </c>
       <c r="B22" t="n">
-        <v>79334</v>
+        <v>91970</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2691,21 +2626,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2715,10 +2650,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>482789</v>
+        <v>482950</v>
       </c>
       <c r="R22" t="n">
-        <v>7039936</v>
+        <v>7040233</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2777,10 +2712,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133099228</v>
+        <v>133099293</v>
       </c>
       <c r="B23" t="n">
-        <v>91928</v>
+        <v>91970</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2788,21 +2723,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2812,10 +2747,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>482716</v>
+        <v>482694</v>
       </c>
       <c r="R23" t="n">
-        <v>7040073</v>
+        <v>7040076</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2874,10 +2809,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133099295</v>
+        <v>133098975</v>
       </c>
       <c r="B24" t="n">
-        <v>91942</v>
+        <v>91974</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2885,21 +2820,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2909,10 +2844,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>482699</v>
+        <v>482788</v>
       </c>
       <c r="R24" t="n">
-        <v>7040083</v>
+        <v>7040091</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2971,10 +2906,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133099020</v>
+        <v>133098977</v>
       </c>
       <c r="B25" t="n">
-        <v>91924</v>
+        <v>91974</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2982,21 +2917,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3006,10 +2941,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>482765</v>
+        <v>482880</v>
       </c>
       <c r="R25" t="n">
-        <v>7039995</v>
+        <v>7040042</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3068,10 +3003,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133099289</v>
+        <v>133098979</v>
       </c>
       <c r="B26" t="n">
-        <v>91924</v>
+        <v>91974</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3079,21 +3014,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3103,10 +3038,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>483011</v>
+        <v>482794</v>
       </c>
       <c r="R26" t="n">
-        <v>7040039</v>
+        <v>7039988</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3165,32 +3100,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133098980</v>
+        <v>133099220</v>
       </c>
       <c r="B27" t="n">
-        <v>92651</v>
+        <v>91974</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3200,10 +3135,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>482862</v>
+        <v>482743</v>
       </c>
       <c r="R27" t="n">
-        <v>7040063</v>
+        <v>7040082</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3262,10 +3197,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133099257</v>
+        <v>133099221</v>
       </c>
       <c r="B28" t="n">
-        <v>57975</v>
+        <v>91974</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3273,21 +3208,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3297,10 +3232,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>482822</v>
+        <v>483042</v>
       </c>
       <c r="R28" t="n">
-        <v>7039997</v>
+        <v>7040216</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3333,11 +3268,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2026-05-03</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3364,10 +3294,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133099237</v>
+        <v>133099222</v>
       </c>
       <c r="B29" t="n">
-        <v>57975</v>
+        <v>91974</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3375,21 +3305,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3399,10 +3329,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>482767</v>
+        <v>483027</v>
       </c>
       <c r="R29" t="n">
-        <v>7040511</v>
+        <v>7040129</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3435,11 +3365,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2026-05-03</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3466,10 +3391,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133099236</v>
+        <v>133099223</v>
       </c>
       <c r="B30" t="n">
-        <v>57975</v>
+        <v>91974</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3477,21 +3402,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3501,10 +3426,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>482762</v>
+        <v>483039</v>
       </c>
       <c r="R30" t="n">
-        <v>7040506</v>
+        <v>7040041</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3537,11 +3462,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2026-05-03</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3568,10 +3488,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133098997</v>
+        <v>133099225</v>
       </c>
       <c r="B31" t="n">
-        <v>57975</v>
+        <v>91974</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3579,21 +3499,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3603,10 +3523,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>483020</v>
+        <v>482822</v>
       </c>
       <c r="R31" t="n">
-        <v>7040126</v>
+        <v>7040006</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3639,11 +3559,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2026-05-03</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3670,10 +3585,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133099019</v>
+        <v>133099226</v>
       </c>
       <c r="B32" t="n">
-        <v>91924</v>
+        <v>91974</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3681,21 +3596,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3705,10 +3620,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>482859</v>
+        <v>482787</v>
       </c>
       <c r="R32" t="n">
-        <v>7039916</v>
+        <v>7040007</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3767,10 +3682,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>133099259</v>
+        <v>133099227</v>
       </c>
       <c r="B33" t="n">
-        <v>58119</v>
+        <v>91974</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3778,50 +3693,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Johanssonsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>483024</v>
+        <v>482742</v>
       </c>
       <c r="R33" t="n">
-        <v>7040025</v>
+        <v>7040066</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3880,10 +3779,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133099018</v>
+        <v>133099228</v>
       </c>
       <c r="B34" t="n">
-        <v>91924</v>
+        <v>91974</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3891,21 +3790,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3915,10 +3814,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>482859</v>
+        <v>482716</v>
       </c>
       <c r="R34" t="n">
-        <v>7040251</v>
+        <v>7040073</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3977,10 +3876,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133098977</v>
+        <v>133099229</v>
       </c>
       <c r="B35" t="n">
-        <v>91928</v>
+        <v>91974</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4012,10 +3911,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>482880</v>
+        <v>482859</v>
       </c>
       <c r="R35" t="n">
-        <v>7040042</v>
+        <v>7040276</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4074,32 +3973,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133099244</v>
+        <v>133099023</v>
       </c>
       <c r="B36" t="n">
-        <v>57975</v>
+        <v>91988</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4109,10 +4008,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>482734</v>
+        <v>482930</v>
       </c>
       <c r="R36" t="n">
-        <v>7040454</v>
+        <v>7040057</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4145,11 +4044,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2026-05-03</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4176,32 +4070,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133099252</v>
+        <v>133099024</v>
       </c>
       <c r="B37" t="n">
-        <v>57975</v>
+        <v>91988</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4211,10 +4105,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>483047</v>
+        <v>482910</v>
       </c>
       <c r="R37" t="n">
-        <v>7040061</v>
+        <v>7040052</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4247,11 +4141,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2026-05-03</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4278,32 +4167,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133098983</v>
+        <v>133099295</v>
       </c>
       <c r="B38" t="n">
-        <v>57975</v>
+        <v>91988</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4313,10 +4202,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>482911</v>
+        <v>482699</v>
       </c>
       <c r="R38" t="n">
-        <v>7040096</v>
+        <v>7040083</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4349,11 +4238,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2026-05-03</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4380,32 +4264,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133099293</v>
+        <v>133099296</v>
       </c>
       <c r="B39" t="n">
-        <v>91924</v>
+        <v>91988</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1108</v>
+        <v>1204</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4415,10 +4299,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>482694</v>
+        <v>482977</v>
       </c>
       <c r="R39" t="n">
-        <v>7040076</v>
+        <v>7040365</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4477,10 +4361,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133099219</v>
+        <v>133099297</v>
       </c>
       <c r="B40" t="n">
-        <v>92300</v>
+        <v>91988</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4488,21 +4372,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2062</v>
+        <v>1204</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4512,10 +4396,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>482826</v>
+        <v>482745</v>
       </c>
       <c r="R40" t="n">
-        <v>7039980</v>
+        <v>7040056</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4548,11 +4432,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2026-05-03</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Brevispora</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4579,32 +4458,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>133098981</v>
+        <v>133099276</v>
       </c>
       <c r="B41" t="n">
-        <v>92651</v>
+        <v>92406</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>3298</v>
+        <v>1209</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4614,10 +4493,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>482925</v>
+        <v>483033</v>
       </c>
       <c r="R41" t="n">
-        <v>7040278</v>
+        <v>7040201</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4676,32 +4555,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>133099217</v>
+        <v>133099219</v>
       </c>
       <c r="B42" t="n">
-        <v>91891</v>
+        <v>92318</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5447</v>
+        <v>2062</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4711,10 +4590,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>483038</v>
+        <v>482826</v>
       </c>
       <c r="R42" t="n">
-        <v>7040049</v>
+        <v>7039980</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4747,6 +4626,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Brevispora</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4773,32 +4657,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>133099248</v>
+        <v>133098980</v>
       </c>
       <c r="B43" t="n">
-        <v>57975</v>
+        <v>92199</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4808,10 +4692,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>482969</v>
+        <v>482862</v>
       </c>
       <c r="R43" t="n">
-        <v>7040373</v>
+        <v>7040063</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4844,11 +4728,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2026-05-03</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4875,10 +4754,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>133099233</v>
+        <v>133098981</v>
       </c>
       <c r="B44" t="n">
-        <v>92651</v>
+        <v>92199</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4910,10 +4789,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>482792</v>
+        <v>482925</v>
       </c>
       <c r="R44" t="n">
-        <v>7039995</v>
+        <v>7040278</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4972,32 +4851,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>133099307</v>
+        <v>133099231</v>
       </c>
       <c r="B45" t="n">
-        <v>83311</v>
+        <v>92199</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>308</v>
+        <v>3298</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5007,10 +4886,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>482915</v>
+        <v>482934</v>
       </c>
       <c r="R45" t="n">
-        <v>7040050</v>
+        <v>7040260</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5069,32 +4948,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>133098979</v>
+        <v>133099232</v>
       </c>
       <c r="B46" t="n">
-        <v>91928</v>
+        <v>92199</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5104,10 +4983,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>482794</v>
+        <v>482820</v>
       </c>
       <c r="R46" t="n">
-        <v>7039988</v>
+        <v>7040003</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5166,32 +5045,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>133099249</v>
+        <v>133099233</v>
       </c>
       <c r="B47" t="n">
-        <v>57975</v>
+        <v>92199</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5201,10 +5080,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>483025</v>
+        <v>482792</v>
       </c>
       <c r="R47" t="n">
-        <v>7040275</v>
+        <v>7039995</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5237,11 +5116,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2026-05-03</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5268,10 +5142,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>133099025</v>
+        <v>133099217</v>
       </c>
       <c r="B48" t="n">
-        <v>101348</v>
+        <v>91937</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5279,21 +5153,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>222498</v>
+        <v>5447</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5303,10 +5177,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>482983</v>
+        <v>483038</v>
       </c>
       <c r="R48" t="n">
-        <v>7040302</v>
+        <v>7040049</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5365,32 +5239,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>133099223</v>
+        <v>133099218</v>
       </c>
       <c r="B49" t="n">
-        <v>91928</v>
+        <v>91937</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5400,10 +5274,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>483039</v>
+        <v>482924</v>
       </c>
       <c r="R49" t="n">
-        <v>7040041</v>
+        <v>7040053</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5462,14 +5336,14 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>133099300</v>
+        <v>133099298</v>
       </c>
       <c r="B50" t="n">
-        <v>79334</v>
+        <v>79373</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
@@ -5497,10 +5371,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>483070</v>
+        <v>482824</v>
       </c>
       <c r="R50" t="n">
-        <v>7040173</v>
+        <v>7040124</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5533,6 +5407,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Rikligt &gt;500 bålar</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5559,32 +5438,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>133099280</v>
+        <v>133099299</v>
       </c>
       <c r="B51" t="n">
-        <v>78346</v>
+        <v>79373</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5594,10 +5473,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>482803</v>
+        <v>482745</v>
       </c>
       <c r="R51" t="n">
-        <v>7039944</v>
+        <v>7040437</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5630,6 +5509,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Rikligt &gt;200 bålar</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5656,32 +5540,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>133099290</v>
+        <v>133099300</v>
       </c>
       <c r="B52" t="n">
-        <v>91924</v>
+        <v>79373</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5691,10 +5575,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>482948</v>
+        <v>483070</v>
       </c>
       <c r="R52" t="n">
-        <v>7040035</v>
+        <v>7040173</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5753,32 +5637,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>133099222</v>
+        <v>133099301</v>
       </c>
       <c r="B53" t="n">
-        <v>91928</v>
+        <v>79373</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5788,10 +5672,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>483027</v>
+        <v>483043</v>
       </c>
       <c r="R53" t="n">
-        <v>7040129</v>
+        <v>7040056</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5850,32 +5734,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>133099235</v>
+        <v>133099302</v>
       </c>
       <c r="B54" t="n">
-        <v>57975</v>
+        <v>79373</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5885,10 +5769,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>482750</v>
+        <v>482877</v>
       </c>
       <c r="R54" t="n">
-        <v>7040130</v>
+        <v>7039972</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5925,7 +5809,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gran</t>
+          <t>Rikligt &gt; 100 bålar</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -5952,32 +5836,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>133098984</v>
+        <v>133099304</v>
       </c>
       <c r="B55" t="n">
-        <v>57975</v>
+        <v>79373</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5987,10 +5871,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>482818</v>
+        <v>482789</v>
       </c>
       <c r="R55" t="n">
-        <v>7040229</v>
+        <v>7039936</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6023,11 +5907,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2026-05-03</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6054,32 +5933,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>133099225</v>
+        <v>133099305</v>
       </c>
       <c r="B56" t="n">
-        <v>91928</v>
+        <v>79373</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6089,10 +5968,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>482822</v>
+        <v>482848</v>
       </c>
       <c r="R56" t="n">
-        <v>7040006</v>
+        <v>7039978</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6151,32 +6030,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>133099216</v>
+        <v>133099306</v>
       </c>
       <c r="B57" t="n">
-        <v>97380</v>
+        <v>79373</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6186,10 +6065,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>482737</v>
+        <v>482783</v>
       </c>
       <c r="R57" t="n">
-        <v>7040092</v>
+        <v>7040050</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6248,10 +6127,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>133099292</v>
+        <v>133099214</v>
       </c>
       <c r="B58" t="n">
-        <v>91924</v>
+        <v>83358</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6259,21 +6138,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1108</v>
+        <v>6440</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6283,10 +6162,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>482950</v>
+        <v>482802</v>
       </c>
       <c r="R58" t="n">
-        <v>7040233</v>
+        <v>7039942</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6345,10 +6224,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>133099256</v>
+        <v>133099215</v>
       </c>
       <c r="B59" t="n">
-        <v>57975</v>
+        <v>83358</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6356,21 +6235,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6380,10 +6259,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>482818</v>
+        <v>482800</v>
       </c>
       <c r="R59" t="n">
-        <v>7040002</v>
+        <v>7039924</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6416,11 +6295,6 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2026-05-03</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6447,7 +6321,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>133099243</v>
+        <v>133098983</v>
       </c>
       <c r="B60" t="n">
         <v>57975</v>
@@ -6482,10 +6356,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>482737</v>
+        <v>482911</v>
       </c>
       <c r="R60" t="n">
-        <v>7040464</v>
+        <v>7040096</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6522,7 +6396,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Färska ringhack på gran</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6549,10 +6423,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>133099221</v>
+        <v>133098984</v>
       </c>
       <c r="B61" t="n">
-        <v>91928</v>
+        <v>57975</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6560,21 +6434,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6584,10 +6458,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>483042</v>
+        <v>482818</v>
       </c>
       <c r="R61" t="n">
-        <v>7040216</v>
+        <v>7040229</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6620,6 +6494,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6646,32 +6525,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>133099276</v>
+        <v>133098986</v>
       </c>
       <c r="B62" t="n">
-        <v>92388</v>
+        <v>57975</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6681,10 +6560,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>483033</v>
+        <v>482755</v>
       </c>
       <c r="R62" t="n">
-        <v>7040201</v>
+        <v>7040271</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6717,6 +6596,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6743,10 +6627,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>133099283</v>
+        <v>133098987</v>
       </c>
       <c r="B63" t="n">
-        <v>91924</v>
+        <v>57975</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6754,21 +6638,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6778,10 +6662,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>482817</v>
+        <v>482747</v>
       </c>
       <c r="R63" t="n">
-        <v>7040296</v>
+        <v>7040142</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6814,6 +6698,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6840,10 +6729,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>133099021</v>
+        <v>133098989</v>
       </c>
       <c r="B64" t="n">
-        <v>91924</v>
+        <v>57975</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6851,21 +6740,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6875,10 +6764,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>482718</v>
+        <v>482742</v>
       </c>
       <c r="R64" t="n">
-        <v>7040049</v>
+        <v>7040155</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6911,6 +6800,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -6937,7 +6831,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>133099253</v>
+        <v>133098990</v>
       </c>
       <c r="B65" t="n">
         <v>57975</v>
@@ -6972,10 +6866,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>482940</v>
+        <v>482726</v>
       </c>
       <c r="R65" t="n">
-        <v>7040118</v>
+        <v>7040169</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7012,7 +6906,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gran</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7039,10 +6933,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>133099214</v>
+        <v>133098991</v>
       </c>
       <c r="B66" t="n">
-        <v>83319</v>
+        <v>57975</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7050,21 +6944,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7074,10 +6968,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>482802</v>
+        <v>482715</v>
       </c>
       <c r="R66" t="n">
-        <v>7039942</v>
+        <v>7040181</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7110,6 +7004,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7136,32 +7035,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>133099232</v>
+        <v>133098993</v>
       </c>
       <c r="B67" t="n">
-        <v>92651</v>
+        <v>57975</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7171,10 +7070,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>482820</v>
+        <v>482790</v>
       </c>
       <c r="R67" t="n">
-        <v>7040003</v>
+        <v>7040409</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7207,6 +7106,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7233,10 +7137,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>133099279</v>
+        <v>133098994</v>
       </c>
       <c r="B68" t="n">
-        <v>92227</v>
+        <v>57975</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7244,21 +7148,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7268,10 +7172,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>483036</v>
+        <v>482761</v>
       </c>
       <c r="R68" t="n">
-        <v>7040043</v>
+        <v>7040430</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7304,6 +7208,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7330,10 +7239,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>133099226</v>
+        <v>133098996</v>
       </c>
       <c r="B69" t="n">
-        <v>91928</v>
+        <v>57975</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7341,34 +7250,54 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Johanssonsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>482787</v>
+        <v>482964</v>
       </c>
       <c r="R69" t="n">
-        <v>7040007</v>
+        <v>7040289</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7401,6 +7330,11 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Trummande födosökande hona</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7427,10 +7361,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>133099227</v>
+        <v>133098997</v>
       </c>
       <c r="B70" t="n">
-        <v>91928</v>
+        <v>57975</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7438,21 +7372,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7462,10 +7396,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>482742</v>
+        <v>483020</v>
       </c>
       <c r="R70" t="n">
-        <v>7040066</v>
+        <v>7040126</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7498,6 +7432,11 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7524,7 +7463,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>133099258</v>
+        <v>133098999</v>
       </c>
       <c r="B71" t="n">
         <v>57975</v>
@@ -7553,16 +7492,24 @@
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Johanssonsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>482797</v>
+        <v>482821</v>
       </c>
       <c r="R71" t="n">
-        <v>7040018</v>
+        <v>7039982</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7599,7 +7546,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Färska ringhack på gran</t>
+          <t>Bohål ca 2,1m upp i tajgagrantickerötad granhögstubbe</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7728,7 +7675,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>133099241</v>
+        <v>133099234</v>
       </c>
       <c r="B73" t="n">
         <v>57975</v>
@@ -7763,10 +7710,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>482746</v>
+        <v>482759</v>
       </c>
       <c r="R73" t="n">
-        <v>7040486</v>
+        <v>7040108</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7803,7 +7750,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Färska ringhack på gran</t>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7830,7 +7777,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>133099238</v>
+        <v>133099235</v>
       </c>
       <c r="B74" t="n">
         <v>57975</v>
@@ -7865,10 +7812,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>482774</v>
+        <v>482750</v>
       </c>
       <c r="R74" t="n">
-        <v>7040500</v>
+        <v>7040130</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7905,7 +7852,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Färska ringhack på gran</t>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -7932,10 +7879,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>133099291</v>
+        <v>133099236</v>
       </c>
       <c r="B75" t="n">
-        <v>91924</v>
+        <v>57975</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7943,21 +7890,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7967,10 +7914,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>482854</v>
+        <v>482762</v>
       </c>
       <c r="R75" t="n">
-        <v>7039929</v>
+        <v>7040506</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8003,6 +7950,11 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8029,10 +7981,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>133099285</v>
+        <v>133099237</v>
       </c>
       <c r="B76" t="n">
-        <v>91924</v>
+        <v>57975</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8040,21 +7992,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8064,10 +8016,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>483006</v>
+        <v>482767</v>
       </c>
       <c r="R76" t="n">
-        <v>7040340</v>
+        <v>7040511</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8100,6 +8052,11 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8126,32 +8083,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>133099275</v>
+        <v>133099238</v>
       </c>
       <c r="B77" t="n">
-        <v>83310</v>
+        <v>57975</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>492</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8161,10 +8118,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>482908</v>
+        <v>482774</v>
       </c>
       <c r="R77" t="n">
-        <v>7040032</v>
+        <v>7040500</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8197,6 +8154,11 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8223,10 +8185,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>133099229</v>
+        <v>133099239</v>
       </c>
       <c r="B78" t="n">
-        <v>91928</v>
+        <v>57975</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8234,21 +8196,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8258,10 +8220,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>482859</v>
+        <v>482757</v>
       </c>
       <c r="R78" t="n">
-        <v>7040276</v>
+        <v>7040498</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8294,6 +8256,11 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8320,10 +8287,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>133099302</v>
+        <v>133099240</v>
       </c>
       <c r="B79" t="n">
-        <v>79334</v>
+        <v>57975</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8331,21 +8298,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8355,10 +8322,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>482877</v>
+        <v>482749</v>
       </c>
       <c r="R79" t="n">
-        <v>7039972</v>
+        <v>7040493</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8395,7 +8362,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Rikligt &gt; 100 bålar</t>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8422,7 +8389,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>133099255</v>
+        <v>133099241</v>
       </c>
       <c r="B80" t="n">
         <v>57975</v>
@@ -8457,10 +8424,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>482828</v>
+        <v>482746</v>
       </c>
       <c r="R80" t="n">
-        <v>7039997</v>
+        <v>7040486</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8497,7 +8464,7 @@
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gran</t>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8626,10 +8593,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>133098975</v>
+        <v>133099243</v>
       </c>
       <c r="B82" t="n">
-        <v>91928</v>
+        <v>57975</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8637,21 +8604,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8661,10 +8628,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>482788</v>
+        <v>482737</v>
       </c>
       <c r="R82" t="n">
-        <v>7040091</v>
+        <v>7040464</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8697,6 +8664,11 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8723,10 +8695,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>133099024</v>
+        <v>133099244</v>
       </c>
       <c r="B83" t="n">
-        <v>91942</v>
+        <v>57975</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8734,21 +8706,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8758,10 +8730,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>482910</v>
+        <v>482734</v>
       </c>
       <c r="R83" t="n">
-        <v>7040052</v>
+        <v>7040454</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8794,6 +8766,11 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -8820,7 +8797,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>133099251</v>
+        <v>133099245</v>
       </c>
       <c r="B84" t="n">
         <v>57975</v>
@@ -8855,10 +8832,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>483015</v>
+        <v>482765</v>
       </c>
       <c r="R84" t="n">
-        <v>7040129</v>
+        <v>7040428</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8895,7 +8872,7 @@
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>Färska ringhack på gran</t>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -8922,10 +8899,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>133099288</v>
+        <v>133099246</v>
       </c>
       <c r="B85" t="n">
-        <v>91924</v>
+        <v>57975</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8933,21 +8910,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8957,10 +8934,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>483034</v>
+        <v>482890</v>
       </c>
       <c r="R85" t="n">
-        <v>7040042</v>
+        <v>7040433</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8993,6 +8970,11 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9019,7 +9001,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>133099240</v>
+        <v>133099247</v>
       </c>
       <c r="B86" t="n">
         <v>57975</v>
@@ -9048,16 +9030,24 @@
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Johanssonsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>482749</v>
+        <v>482949</v>
       </c>
       <c r="R86" t="n">
-        <v>7040493</v>
+        <v>7040385</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9094,7 +9084,7 @@
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gran</t>
+          <t>Äldre bohål på tajgagrantickerötad gran</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9121,10 +9111,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>133099247</v>
+        <v>133099248</v>
       </c>
       <c r="B87" t="n">
-        <v>57958</v>
+        <v>57975</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9150,24 +9140,16 @@
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Johanssonsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>482949</v>
+        <v>482969</v>
       </c>
       <c r="R87" t="n">
-        <v>7040385</v>
+        <v>7040373</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9204,7 +9186,7 @@
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>Äldre bohål på tajgagrantickerötad gran</t>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9231,10 +9213,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>133098999</v>
+        <v>133099249</v>
       </c>
       <c r="B88" t="n">
-        <v>57958</v>
+        <v>57975</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9260,24 +9242,16 @@
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Johanssonsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>482821</v>
+        <v>483025</v>
       </c>
       <c r="R88" t="n">
-        <v>7039982</v>
+        <v>7040275</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9314,7 +9288,7 @@
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>Bohål ca 2,1m upp i tajgagrantickerötad granhögstubbe</t>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9463,10 +9437,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>133099215</v>
+        <v>133099251</v>
       </c>
       <c r="B90" t="n">
-        <v>83319</v>
+        <v>57975</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9474,21 +9448,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9498,10 +9472,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>482800</v>
+        <v>483015</v>
       </c>
       <c r="R90" t="n">
-        <v>7039924</v>
+        <v>7040129</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9534,6 +9508,11 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9560,10 +9539,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>133099277</v>
+        <v>133099252</v>
       </c>
       <c r="B91" t="n">
-        <v>92227</v>
+        <v>57975</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9571,21 +9550,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9595,10 +9574,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>482910</v>
+        <v>483047</v>
       </c>
       <c r="R91" t="n">
-        <v>7040174</v>
+        <v>7040061</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9631,6 +9610,11 @@
       <c r="AA91" t="inlineStr">
         <is>
           <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9657,10 +9641,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>133099298</v>
+        <v>133099253</v>
       </c>
       <c r="B92" t="n">
-        <v>79334</v>
+        <v>57975</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9668,21 +9652,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9692,10 +9676,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>482824</v>
+        <v>482940</v>
       </c>
       <c r="R92" t="n">
-        <v>7040124</v>
+        <v>7040118</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9732,7 +9716,7 @@
       </c>
       <c r="AC92" t="inlineStr">
         <is>
-          <t>Rikligt &gt;500 bålar</t>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9759,10 +9743,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>133099299</v>
+        <v>133099254</v>
       </c>
       <c r="B93" t="n">
-        <v>79334</v>
+        <v>57975</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9770,21 +9754,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9794,10 +9778,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>482745</v>
+        <v>482812</v>
       </c>
       <c r="R93" t="n">
-        <v>7040437</v>
+        <v>7039935</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9834,7 +9818,7 @@
       </c>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>Rikligt &gt;200 bålar</t>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -9861,10 +9845,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>133099301</v>
+        <v>133099255</v>
       </c>
       <c r="B94" t="n">
-        <v>79334</v>
+        <v>57975</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9872,21 +9856,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9896,10 +9880,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>483043</v>
+        <v>482828</v>
       </c>
       <c r="R94" t="n">
-        <v>7040056</v>
+        <v>7039997</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9932,6 +9916,11 @@
       <c r="AA94" t="inlineStr">
         <is>
           <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -9958,7 +9947,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>133099234</v>
+        <v>133099256</v>
       </c>
       <c r="B95" t="n">
         <v>57975</v>
@@ -9993,10 +9982,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>482759</v>
+        <v>482818</v>
       </c>
       <c r="R95" t="n">
-        <v>7040108</v>
+        <v>7040002</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10060,7 +10049,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>133098994</v>
+        <v>133099257</v>
       </c>
       <c r="B96" t="n">
         <v>57975</v>
@@ -10095,10 +10084,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>482761</v>
+        <v>482822</v>
       </c>
       <c r="R96" t="n">
-        <v>7040430</v>
+        <v>7039997</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10135,7 +10124,7 @@
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10162,7 +10151,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>133098990</v>
+        <v>133099258</v>
       </c>
       <c r="B97" t="n">
         <v>57975</v>
@@ -10197,10 +10186,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>482726</v>
+        <v>482797</v>
       </c>
       <c r="R97" t="n">
-        <v>7040169</v>
+        <v>7040018</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10237,7 +10226,7 @@
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10267,11 +10256,11 @@
         <v>133099282</v>
       </c>
       <c r="B98" t="n">
-        <v>57136</v>
+        <v>57153</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
@@ -10361,45 +10350,61 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>133099281</v>
+        <v>133099259</v>
       </c>
       <c r="B99" t="n">
-        <v>80399</v>
+        <v>58136</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>229497</v>
+        <v>103021</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Johanssonsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>482905</v>
+        <v>483024</v>
       </c>
       <c r="R99" t="n">
-        <v>7040145</v>
+        <v>7040025</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10458,32 +10463,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>133099254</v>
+        <v>133099025</v>
       </c>
       <c r="B100" t="n">
-        <v>57975</v>
+        <v>101403</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10493,10 +10498,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>482812</v>
+        <v>482983</v>
       </c>
       <c r="R100" t="n">
-        <v>7039935</v>
+        <v>7040302</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10529,11 +10534,6 @@
       <c r="AA100" t="inlineStr">
         <is>
           <t>2026-05-03</t>
-        </is>
-      </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10560,10 +10560,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>133099287</v>
+        <v>133099280</v>
       </c>
       <c r="B101" t="n">
-        <v>91924</v>
+        <v>78382</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10571,21 +10571,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>1108</v>
+        <v>228579</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10595,10 +10595,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>483086</v>
+        <v>482803</v>
       </c>
       <c r="R101" t="n">
-        <v>7040200</v>
+        <v>7039944</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10657,32 +10657,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>133099296</v>
+        <v>133099281</v>
       </c>
       <c r="B102" t="n">
-        <v>91942</v>
+        <v>80438</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>1204</v>
+        <v>229497</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10692,10 +10692,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>482977</v>
+        <v>482905</v>
       </c>
       <c r="R102" t="n">
-        <v>7040365</v>
+        <v>7040145</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>

--- a/artfynd/A 16101-2026 artfynd.xlsx
+++ b/artfynd/A 16101-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY102"/>
+  <dimension ref="A1:AZ102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133099216</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133099274</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133099307</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133099308</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133099309</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133099275</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133099277</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133099279</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133099311</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133099018</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133099019</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133099020</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,6 +1998,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133099021</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2030,6 +2100,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133099283</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2127,6 +2202,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133099285</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2224,6 +2304,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133099287</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2321,6 +2406,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133099288</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2418,6 +2508,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133099289</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2515,6 +2610,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133099290</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2612,6 +2712,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133099291</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2709,6 +2814,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133099292</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2806,6 +2916,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133099293</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2903,6 +3018,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133098975</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3000,6 +3120,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133098977</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3097,6 +3222,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133098979</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3194,6 +3324,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133099220</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3291,6 +3426,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133099221</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3388,6 +3528,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133099222</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3485,6 +3630,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133099223</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3582,6 +3732,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133099225</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3679,6 +3834,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133099226</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3776,6 +3936,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133099227</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3873,6 +4038,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133099228</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3970,6 +4140,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133099229</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4067,6 +4242,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133099023</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4164,6 +4344,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133099024</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4261,6 +4446,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133099295</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4358,6 +4548,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133099296</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4455,6 +4650,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133099297</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4552,6 +4752,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133099276</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4654,6 +4859,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133099219</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4751,6 +4961,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133098980</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4848,6 +5063,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133098981</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -4945,6 +5165,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133099231</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5042,6 +5267,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133099232</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5139,6 +5369,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133099233</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5236,6 +5471,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133099217</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5333,6 +5573,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133099218</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5435,6 +5680,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133099298</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5537,6 +5787,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133099299</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5634,6 +5889,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133099300</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5731,6 +5991,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133099301</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5833,6 +6098,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133099302</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -5930,6 +6200,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133099304</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6027,6 +6302,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133099305</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6124,6 +6404,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133099306</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6221,6 +6506,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133099214</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6318,6 +6608,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133099215</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6420,6 +6715,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133098983</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6522,6 +6822,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133098984</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6624,6 +6929,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133098986</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6726,6 +7036,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133098987</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6828,6 +7143,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133098989</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -6930,6 +7250,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133098990</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7032,6 +7357,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133098991</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7134,6 +7464,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133098993</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7236,6 +7571,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133098994</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7358,6 +7698,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133098996</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7460,6 +7805,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133098997</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7570,6 +7920,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133098999</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7672,6 +8027,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133099002</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7774,6 +8134,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133099234</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -7876,6 +8241,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133099235</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -7978,6 +8348,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133099236</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8080,6 +8455,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133099237</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8182,6 +8562,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133099238</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8284,6 +8669,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133099239</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8386,6 +8776,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133099240</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8488,6 +8883,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133099241</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8590,6 +8990,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133099242</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8692,6 +9097,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133099243</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -8794,6 +9204,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133099244</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -8896,6 +9311,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133099245</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -8998,6 +9418,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133099246</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9108,6 +9533,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133099247</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9210,6 +9640,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133099248</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9312,6 +9747,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133099249</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9434,6 +9874,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133099250</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9536,6 +9981,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133099251</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9638,6 +10088,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133099252</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -9740,6 +10195,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133099253</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -9842,6 +10302,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133099254</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -9944,6 +10409,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133099255</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10046,6 +10516,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133099256</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10148,6 +10623,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133099257</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10250,6 +10730,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133099258</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10347,6 +10832,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133099282</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10460,6 +10950,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133099259</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -10557,6 +11052,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133099025</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -10654,6 +11154,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133099280</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -10751,8 +11256,116 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133099281</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>